--- a/academias/Administración de Recursos Humanos - Estadisticos 20232.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20232.xlsx
@@ -1223,25 +1223,25 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>2.9</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>45</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>31</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1392,25 +1392,25 @@
         <v>111</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>97.3</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>2.7</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1427,25 +1427,25 @@
         <v>25</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J8">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>7.7</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1494,25 +1494,25 @@
         <v>51</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F10">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1596,25 +1596,25 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1631,25 +1631,25 @@
         <v>34</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>20.6</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1666,25 +1666,25 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F15">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>4.4</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1698,25 +1698,25 @@
         <v>114</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="F16">
-        <v>114</v>
+        <v>16</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J16">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1733,25 +1733,25 @@
         <v>34</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>73.5</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>26.5</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="J17">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1768,25 +1768,25 @@
         <v>25</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1800,25 +1800,25 @@
         <v>59</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F19">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>18.6</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1829,25 +1829,25 @@
         <v>392</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F20">
-        <v>392</v>
+        <v>71</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>18.1</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J20">
-        <v>392</v>
+        <v>31</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1915,19 +1915,19 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>96.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>3.8</v>
+        <v>26.9</v>
       </c>
       <c r="I2" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1947,19 +1947,19 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1">
-        <v>96.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>3.8</v>
+        <v>26.9</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1982,19 +1982,19 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="H4" s="1">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="I4" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2017,19 +2017,19 @@
         <v>45</v>
       </c>
       <c r="E5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>93.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>6.7</v>
+        <v>4.4</v>
       </c>
       <c r="I5" s="2">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2064,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2084,19 +2084,19 @@
         <v>111</v>
       </c>
       <c r="E7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>95.5</v>
+        <v>97.3</v>
       </c>
       <c r="H7" s="1">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>25</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H8" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I8" s="2">
         <v>8.800000000000001</v>
@@ -2154,19 +2154,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>96.2</v>
+        <v>92.3</v>
       </c>
       <c r="H9" s="1">
-        <v>3.8</v>
+        <v>7.7</v>
       </c>
       <c r="I9" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2198,7 +2198,7 @@
         <v>5.9</v>
       </c>
       <c r="I10" s="2">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2288,19 +2288,19 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2323,19 +2323,19 @@
         <v>34</v>
       </c>
       <c r="E14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>97.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H14" s="1">
-        <v>2.9</v>
+        <v>20.6</v>
       </c>
       <c r="I14" s="2">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2358,19 +2358,19 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1">
-        <v>97.8</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="I15" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2390,19 +2390,19 @@
         <v>114</v>
       </c>
       <c r="E16">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="F16">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G16" s="1">
-        <v>98.2</v>
+        <v>86</v>
       </c>
       <c r="H16" s="1">
-        <v>1.8</v>
+        <v>14</v>
       </c>
       <c r="I16" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2425,19 +2425,19 @@
         <v>34</v>
       </c>
       <c r="E17">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F17">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1">
-        <v>82.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="H17" s="1">
-        <v>17.6</v>
+        <v>26.5</v>
       </c>
       <c r="I17" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2460,19 +2460,19 @@
         <v>25</v>
       </c>
       <c r="E18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H18" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I18" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2492,19 +2492,19 @@
         <v>59</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G19" s="1">
-        <v>84.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="H19" s="1">
-        <v>15.3</v>
+        <v>18.6</v>
       </c>
       <c r="I19" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2521,16 +2521,16 @@
         <v>392</v>
       </c>
       <c r="E20">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1">
-        <v>94.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="H20" s="1">
-        <v>5.1</v>
+        <v>10.2</v>
       </c>
       <c r="I20" s="2">
         <v>8.199999999999999</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20232.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20232.xlsx
@@ -1529,25 +1529,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1561,25 +1561,25 @@
         <v>31</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1829,25 +1829,25 @@
         <v>392</v>
       </c>
       <c r="E20">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="F20">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="G20" s="1">
-        <v>81.90000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="H20" s="1">
-        <v>18.1</v>
+        <v>10.2</v>
       </c>
       <c r="I20" s="2">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>7.9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2233,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/academias/Administración de Recursos Humanos - Estadisticos 20232.xlsx
+++ b/academias/Administración de Recursos Humanos - Estadisticos 20232.xlsx
@@ -665,10 +665,10 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -697,19 +697,19 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F7">
         <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>95.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I7" s="2">
         <v>8.5</v>
@@ -834,10 +834,10 @@
         <v>28</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -866,10 +866,10 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1134,10 +1134,10 @@
         <v>24</v>
       </c>
       <c r="D20">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E20">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F20">
         <v>20</v>
@@ -1357,10 +1357,10 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -1389,10 +1389,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -1526,10 +1526,10 @@
         <v>28</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -1558,10 +1558,10 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1826,19 +1826,19 @@
         <v>24</v>
       </c>
       <c r="D20">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E20">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F20">
         <v>40</v>
       </c>
       <c r="G20" s="1">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="I20" s="2">
         <v>8</v>
@@ -1915,19 +1915,19 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>73.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H2" s="1">
-        <v>26.9</v>
+        <v>3.8</v>
       </c>
       <c r="I2" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1947,19 +1947,19 @@
         <v>26</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>73.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="H3" s="1">
-        <v>26.9</v>
+        <v>3.8</v>
       </c>
       <c r="I3" s="2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1982,19 +1982,19 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1">
-        <v>97.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H4" s="1">
-        <v>2.9</v>
+        <v>8.6</v>
       </c>
       <c r="I4" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2017,19 +2017,19 @@
         <v>45</v>
       </c>
       <c r="E5">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2049,10 +2049,10 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E7">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -2131,7 +2131,7 @@
         <v>4</v>
       </c>
       <c r="I8" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2154,19 +2154,19 @@
         <v>26</v>
       </c>
       <c r="E9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>92.3</v>
+        <v>88.5</v>
       </c>
       <c r="H9" s="1">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="I9" s="2">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2186,19 +2186,19 @@
         <v>51</v>
       </c>
       <c r="E10">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>94.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="H10" s="1">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2218,10 +2218,10 @@
         <v>28</v>
       </c>
       <c r="D11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -2288,19 +2288,19 @@
         <v>35</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" s="1">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>20</v>
+        <v>11.4</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2323,19 +2323,19 @@
         <v>34</v>
       </c>
       <c r="E14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1">
-        <v>79.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="H14" s="1">
-        <v>20.6</v>
+        <v>11.8</v>
       </c>
       <c r="I14" s="2">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2358,19 +2358,19 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>95.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="H15" s="1">
-        <v>4.4</v>
+        <v>2.2</v>
       </c>
       <c r="I15" s="2">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2390,19 +2390,19 @@
         <v>114</v>
       </c>
       <c r="E16">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F16">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G16" s="1">
-        <v>86</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="H16" s="1">
-        <v>14</v>
+        <v>7.9</v>
       </c>
       <c r="I16" s="2">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2425,19 +2425,19 @@
         <v>34</v>
       </c>
       <c r="E17">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G17" s="1">
-        <v>73.5</v>
+        <v>88.2</v>
       </c>
       <c r="H17" s="1">
-        <v>26.5</v>
+        <v>11.8</v>
       </c>
       <c r="I17" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2460,16 +2460,16 @@
         <v>25</v>
       </c>
       <c r="E18">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H18" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2">
         <v>8.5</v>
@@ -2492,19 +2492,19 @@
         <v>59</v>
       </c>
       <c r="E19">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F19">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G19" s="1">
-        <v>81.40000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="H19" s="1">
-        <v>18.6</v>
+        <v>8.5</v>
       </c>
       <c r="I19" s="2">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>24</v>
       </c>
       <c r="D20">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E20">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="F20">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="G20" s="1">
-        <v>89.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="H20" s="1">
-        <v>10.2</v>
+        <v>5.6</v>
       </c>
       <c r="I20" s="2">
         <v>8.199999999999999</v>
